--- a/test_results/UAT_Test.xlsx
+++ b/test_results/UAT_Test.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
   <si>
     <t>User Acceptance Testing</t>
   </si>
@@ -105,60 +105,77 @@
   <si>
     <t>1. Open app.
  2. Fill in search field: Analisis
- 3. Press enter.</t>
+ 3. Press enter.
+ 4. Click arrow on the right side.</t>
   </si>
   <si>
-    <t>Show a list with max 100 authors of similar thesis name with "Analisis"</t>
+    <t>Show a list of authors of similar thesis name with "Analisis"</t>
   </si>
   <si>
-    <t>"Analisis" appears in the list with max 100 authors of similar thesis name</t>
+    <t>"Analisis" appears in the list of authors of similar thesis name</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
+    <t>UAT-002</t>
+  </si>
+  <si>
+    <t>Search similar thesis filtered by author's program</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 1. Click settings icon.
  2. Select 'Informatics' in filter by programs field
- 3. Click x icon for close.
+ 3. Click x icon for close settings modal.
+ 4. Fill in search field: Analisis
+ 5. Press enter.
+ 6. Click arrow on the right side.</t>
+  </si>
+  <si>
+    <t>Show a list of authors that only informatics lecturer who had similar thesis name with "Analisis"</t>
+  </si>
+  <si>
+    <t>UAT-003</t>
+  </si>
+  <si>
+    <t>Searching for similar thesis name/papers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Click settings icon.
+ 2. Change search type 'Author' into 'Paper'.
+ 3. Click x icon for close settings modal.
  4. Fill in search field: Analisis
  5. Press enter.</t>
   </si>
   <si>
-    <t>Show a list with max 100 authors that only informatics lecturer who had similar thesis name with "Analisis"</t>
+    <t>Show a list of papers of similar thesis name with "Analisis"</t>
   </si>
   <si>
-    <t>Searching for 100 similar thesis name</t>
+    <t>UAT-004</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1. Click settings icon.
- 2. Change search type 'Author' into 'Paper'.
- 3. Click x icon for close.
- 4. Fill in search field: Analisis
- 5. Press enter.</t>
-  </si>
-  <si>
-    <t>Show a list with max 100 papers of similar thesis name with "Analisis"</t>
-  </si>
-  <si>
-    <t>Searching for 100 similar thesis name using other model</t>
+    <t>Searching for similar thesis name using other model</t>
   </si>
   <si>
     <t xml:space="preserve"> 1. Click settings icon.
  2. Select search type 'Paper'.
  3. Change model into 'all-MiniLM-L6-v2' or 'IndoBERT (Fine-tuned)'
- 3. Click x icon for close.
+ 3. Click x icon for close settings modal.
  4. Fill in search field: Analisis
  5. Press enter.</t>
   </si>
   <si>
-    <t>Searching for only top 5 similar thesis name</t>
+    <t>UAT-005</t>
+  </si>
+  <si>
+    <t>Searching for top 5 similar thesis name</t>
   </si>
   <si>
     <t xml:space="preserve"> 1. Click settings icon.
  2. Select search type 'Paper'.
  3. Select any model
  4. Change Top K input into '5'
- 3. Click x icon for close.
+ 3. Click x icon for close settings modal.
  4. Fill in search field: Analisis
  5. Press enter.</t>
   </si>
@@ -166,12 +183,15 @@
     <t>Show a list with only top 5 papers of similar thesis name with "Analisis"</t>
   </si>
   <si>
+    <t>UAT-006</t>
+  </si>
+  <si>
     <t>Case-insensitive input</t>
   </si>
   <si>
     <t xml:space="preserve"> 1. Click settings icon.
  2. Select search type 'Paper'.
- 3. Click x icon for close.
+ 3. Click x icon for close settings modal.
  4. Fill in search field: Analisa
  5. Press enter.
  6. Compare with Fill in search field: analisa
@@ -187,12 +207,15 @@
     <t>Fail</t>
   </si>
   <si>
+    <t>UAT-007</t>
+  </si>
+  <si>
     <t>Searching authors name by input author name directly</t>
   </si>
   <si>
     <t xml:space="preserve"> 1. Click settings icon.
  2. Select search type 'Author'.
- 3. Click x icon for close.
+ 3. Click x icon for close settings modal.
  4. Fill in search field: Alexander Setiawan
  5. Press enter.</t>
   </si>
@@ -796,22 +819,22 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>32</v>
@@ -838,22 +861,22 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>32</v>
@@ -880,22 +903,22 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>32</v>
@@ -922,22 +945,22 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G6" s="14" t="s">
         <v>32</v>
@@ -964,25 +987,25 @@
     </row>
     <row r="7">
       <c r="A7" s="16" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -1006,25 +1029,25 @@
     </row>
     <row r="8">
       <c r="A8" s="16" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -28818,7 +28841,7 @@
         <v>20</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>24</v>
@@ -28827,7 +28850,7 @@
         <v>25</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1" s="19"/>
       <c r="H1" s="19"/>
@@ -28852,22 +28875,22 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
